--- a/assets/constructions/examples/ctd_mt1.xlsx
+++ b/assets/constructions/examples/ctd_mt1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -649,11 +649,36 @@
           <t>thr_id</t>
         </is>
       </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M121190320-I1.5M</t>
+          <t>M060480120-I1.0M</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -679,7 +704,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>M16.0X1.5</t>
+          <t>M6.0X1.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -689,20 +714,20 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Fine</t>
+          <t>Coarse</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -714,26 +739,26 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>11.9</v>
+        <v>4.8</v>
       </c>
       <c r="U2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
         <v>12</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>h6</t>
-        </is>
-      </c>
-      <c r="W2" t="n">
-        <v>32</v>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
@@ -770,7 +795,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>HA-12</t>
+          <t>HA-6</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -795,42 +820,61 @@
         </is>
       </c>
       <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>312</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="AV2" t="n">
+        <v>3831.55</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>PMK</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7015TF-M12</t>
+          <t>THREAD MILL VR20 Ø9.2 L73 13 UN HM TIALN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ILIX</t>
+          <t>VERGNANO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7015TF</t>
+          <t>VR20 TiAIN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>PMKNS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>M60</t>
+          <t>UN60</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>M60</t>
+          <t>1/2" - 13 UNC</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4H-6H/6G-7G</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,76 +883,70 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+        <v>12.7</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>13</v>
+      </c>
+      <c r="O3" t="n">
+        <v>13</v>
+      </c>
+      <c r="P3" t="n">
+        <v>13</v>
+      </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>BOTH</t>
+          <t>BLIND</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>12</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
       <c r="W3" t="n">
-        <v>21.8</v>
+        <v>22.5</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>21.8</v>
+        <v>22.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>TiAlN</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>K 20</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>K 20</t>
-        </is>
-      </c>
+          <t>TIALN</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
           <t>VHM</t>
         </is>
       </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr">
         <is>
           <t>HA</t>
@@ -916,7 +954,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>HA-12</t>
+          <t>HA-10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -926,7 +964,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr"/>
@@ -937,25 +975,36 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2019/ilix_katalog_taps.pdf</t>
+          <t>2022 / Vergnano-Thread-Mills</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R217.35C140160AC31N 1630</t>
+          <t>H06059L066-I0.6TAP55TMVTH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CoroMillⓇ Plura solid carbide end mill for thread milling</t>
+          <t>Helical</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -966,12 +1015,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UN60</t>
+          <t>VP55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3/4-16 UNF</t>
+          <t>Fine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -985,14 +1034,18 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
-        <v>16</v>
-      </c>
+        <v>5.9</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
@@ -1002,49 +1055,43 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>14</v>
+        <v>5.9</v>
       </c>
       <c r="U4" t="n">
-        <v>14</v>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>h6</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>31.75</v>
+        <v>6.6</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>31.75</v>
+        <v>6.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>83</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>50.4</v>
+      </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>PVD TIALN</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>HC</t>
-        </is>
-      </c>
+          <t>TiAlN</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>VTH</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1052,9 +1099,7 @@
           <t>VHM</t>
         </is>
       </c>
-      <c r="AH4" t="n">
-        <v>10</v>
-      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
         <is>
           <t>HA</t>
@@ -1062,7 +1107,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>HA-14</t>
+          <t>HA-6</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1072,34 +1117,45 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>COROMANT</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>80000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.168</v>
-      </c>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>2021/www.sandvik.coromant.com</t>
+          <t>2018/VARGUS2018-ENGweb.pdf</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>188.9</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AV4" t="n">
+        <v>17366.28</v>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HCF10099L27-EI19BSPTM5VTH</t>
+          <t>HCF20199L52-I8UNTM5VTH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1116,17 +1172,17 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BSPT55</t>
+          <t>UN60</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>R 1/4</t>
+          <t>1" - 8 UNC</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Medium class</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1135,19 +1191,19 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13.157</v>
+        <v>25.4</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -1159,21 +1215,21 @@
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>9.9</v>
+        <v>19.9</v>
       </c>
       <c r="U5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>27.4</v>
+        <v>52.4</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>27.4</v>
+        <v>52.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
@@ -1206,7 +1262,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>HA-10</t>
+          <t>HA-20</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1221,7 +1277,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>ISO228/1:1982</t>
+          <t>ANSI B1.1</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr"/>
@@ -1235,11 +1291,30 @@
         </is>
       </c>
       <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>929.85</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AV5" t="n">
+        <v>85484.55</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L4212680</t>
+          <t>L4212610</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1265,7 +1340,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>M18x1</t>
+          <t>M16x1,5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1279,10 +1354,10 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -1296,24 +1371,24 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="U6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>28</v>
+        <v>25.5</v>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
-        <v>28</v>
+        <v>25.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="n">
@@ -1344,7 +1419,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>HA-14</t>
+          <t>HA-12</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1369,6 +1444,25 @@
         </is>
       </c>
       <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>383.72</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>35276.8</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
